--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S291"/>
+  <dimension ref="A1:S292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18700,49 +18700,49 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>174.76</v>
+        <v>171.63</v>
       </c>
       <c r="C291" t="n">
-        <v>167.01</v>
+        <v>163.46</v>
       </c>
       <c r="D291" t="n">
         <v>163.26</v>
       </c>
       <c r="E291" t="n">
-        <v>157.17</v>
+        <v>153.56</v>
       </c>
       <c r="F291" t="n">
-        <v>158.71</v>
+        <v>155.42</v>
       </c>
       <c r="G291" t="n">
-        <v>155.26</v>
+        <v>153.1</v>
       </c>
       <c r="H291" t="n">
         <v>150.63</v>
       </c>
       <c r="I291" t="n">
-        <v>158.08</v>
+        <v>152.31</v>
       </c>
       <c r="J291" t="n">
-        <v>165.02</v>
+        <v>160.24</v>
       </c>
       <c r="K291" t="n">
-        <v>171.14</v>
+        <v>163.55</v>
       </c>
       <c r="L291" t="n">
-        <v>174.45</v>
+        <v>167.31</v>
       </c>
       <c r="M291" t="n">
-        <v>181.84</v>
+        <v>174.58</v>
       </c>
       <c r="N291" t="n">
         <v>167.97</v>
       </c>
       <c r="O291" t="n">
-        <v>175.66</v>
+        <v>167.41</v>
       </c>
       <c r="P291" t="n">
-        <v>175.31</v>
+        <v>169.55</v>
       </c>
       <c r="Q291" t="n">
         <v>172.47</v>
@@ -18751,6 +18751,69 @@
         <v>180.1</v>
       </c>
       <c r="S291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>170.77</v>
+      </c>
+      <c r="C292" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="D292" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="E292" t="n">
+        <v>145.21</v>
+      </c>
+      <c r="F292" t="n">
+        <v>155.11</v>
+      </c>
+      <c r="G292" t="n">
+        <v>158.16</v>
+      </c>
+      <c r="H292" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="I292" t="n">
+        <v>148.63</v>
+      </c>
+      <c r="J292" t="n">
+        <v>153.41</v>
+      </c>
+      <c r="K292" t="n">
+        <v>152.86</v>
+      </c>
+      <c r="L292" t="n">
+        <v>158.15</v>
+      </c>
+      <c r="M292" t="n">
+        <v>163.93</v>
+      </c>
+      <c r="N292" t="n">
+        <v>160.66</v>
+      </c>
+      <c r="O292" t="n">
+        <v>155.03</v>
+      </c>
+      <c r="P292" t="n">
+        <v>161.73</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>170.04</v>
+      </c>
+      <c r="R292" t="n">
+        <v>177.28</v>
+      </c>
+      <c r="S292" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18767,7 +18830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21750,6 +21813,16 @@
       </c>
       <c r="B298" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -21912,28 +21985,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7349316961793776</v>
+        <v>-0.7228505955924062</v>
       </c>
       <c r="J2" t="n">
+        <v>291</v>
+      </c>
+      <c r="K2" t="n">
         <v>290</v>
       </c>
-      <c r="K2" t="n">
-        <v>289</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1128186258265659</v>
+        <v>0.1099198458024514</v>
       </c>
       <c r="M2" t="n">
-        <v>12.62678335343492</v>
+        <v>12.64060558360327</v>
       </c>
       <c r="N2" t="n">
-        <v>235.2292893550152</v>
+        <v>235.358467640048</v>
       </c>
       <c r="O2" t="n">
-        <v>15.3371864875868</v>
+        <v>15.34139718669874</v>
       </c>
       <c r="P2" t="n">
-        <v>169.8996057838029</v>
+        <v>169.7728918569418</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21984,28 +22057,28 @@
         <v>0.0347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8142555259961215</v>
+        <v>-0.8033083837040668</v>
       </c>
       <c r="J3" t="n">
+        <v>291</v>
+      </c>
+      <c r="K3" t="n">
         <v>290</v>
       </c>
-      <c r="K3" t="n">
-        <v>289</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1739942389392309</v>
+        <v>0.1706228564936815</v>
       </c>
       <c r="M3" t="n">
-        <v>10.98850589681171</v>
+        <v>11.00071491381133</v>
       </c>
       <c r="N3" t="n">
-        <v>174.3152838009689</v>
+        <v>174.4854377021252</v>
       </c>
       <c r="O3" t="n">
-        <v>13.20285135116536</v>
+        <v>13.20929361101967</v>
       </c>
       <c r="P3" t="n">
-        <v>166.5465933851152</v>
+        <v>166.4317440492501</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22056,28 +22129,28 @@
         <v>0.0341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5024189847749654</v>
+        <v>-0.4813031668952675</v>
       </c>
       <c r="J4" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K4" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05202133390543073</v>
+        <v>0.0477460308251243</v>
       </c>
       <c r="M4" t="n">
-        <v>12.04827397005271</v>
+        <v>12.09657272850583</v>
       </c>
       <c r="N4" t="n">
-        <v>252.8010846467037</v>
+        <v>255.0359266731301</v>
       </c>
       <c r="O4" t="n">
-        <v>15.89971964050636</v>
+        <v>15.96984429082294</v>
       </c>
       <c r="P4" t="n">
-        <v>155.7688935975922</v>
+        <v>155.5462938478941</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22128,28 +22201,28 @@
         <v>0.0318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3429264859616765</v>
+        <v>-0.3446391600299468</v>
       </c>
       <c r="J5" t="n">
+        <v>291</v>
+      </c>
+      <c r="K5" t="n">
         <v>290</v>
       </c>
-      <c r="K5" t="n">
-        <v>289</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.036509973706636</v>
+        <v>0.03719973633624707</v>
       </c>
       <c r="M5" t="n">
-        <v>10.52928285803026</v>
+        <v>10.484721860077</v>
       </c>
       <c r="N5" t="n">
-        <v>171.8713910709247</v>
+        <v>171.0036259219246</v>
       </c>
       <c r="O5" t="n">
-        <v>13.10997296224995</v>
+        <v>13.07683547047697</v>
       </c>
       <c r="P5" t="n">
-        <v>153.2485477215328</v>
+        <v>153.2663475603853</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22200,28 +22273,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2443943355854952</v>
+        <v>-0.2403750165554847</v>
       </c>
       <c r="J6" t="n">
+        <v>291</v>
+      </c>
+      <c r="K6" t="n">
         <v>290</v>
       </c>
-      <c r="K6" t="n">
-        <v>289</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02347319566785044</v>
+        <v>0.02289495576684197</v>
       </c>
       <c r="M6" t="n">
-        <v>9.584298360221144</v>
+        <v>9.573129864444192</v>
       </c>
       <c r="N6" t="n">
-        <v>137.6131866882497</v>
+        <v>137.1702199063151</v>
       </c>
       <c r="O6" t="n">
-        <v>11.73086470334773</v>
+        <v>11.71196908748973</v>
       </c>
       <c r="P6" t="n">
-        <v>152.597164228646</v>
+        <v>152.5549165995405</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22272,28 +22345,28 @@
         <v>0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1891130200111927</v>
+        <v>-0.1795352456612233</v>
       </c>
       <c r="J7" t="n">
+        <v>291</v>
+      </c>
+      <c r="K7" t="n">
         <v>290</v>
       </c>
-      <c r="K7" t="n">
-        <v>289</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01521508824115259</v>
+        <v>0.01376739567208574</v>
       </c>
       <c r="M7" t="n">
-        <v>9.219104020849501</v>
+        <v>9.231439119151347</v>
       </c>
       <c r="N7" t="n">
-        <v>128.1963326025706</v>
+        <v>128.441904487815</v>
       </c>
       <c r="O7" t="n">
-        <v>11.32238193149174</v>
+        <v>11.33322127586923</v>
       </c>
       <c r="P7" t="n">
-        <v>147.3000640081104</v>
+        <v>147.1996198314412</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22344,28 +22417,28 @@
         <v>0.0674</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06237527891543128</v>
+        <v>-0.03791272887471819</v>
       </c>
       <c r="J8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K8" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00130516201246933</v>
+        <v>0.000474262030037198</v>
       </c>
       <c r="M8" t="n">
-        <v>10.39118725879519</v>
+        <v>10.45915878048231</v>
       </c>
       <c r="N8" t="n">
-        <v>163.6150130568997</v>
+        <v>167.2222734145605</v>
       </c>
       <c r="O8" t="n">
-        <v>12.79120842832684</v>
+        <v>12.93144514022159</v>
       </c>
       <c r="P8" t="n">
-        <v>137.0408639598969</v>
+        <v>136.7829834673171</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22416,28 +22489,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1606861627279961</v>
+        <v>-0.1593718695555785</v>
       </c>
       <c r="J9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01098412800875626</v>
+        <v>0.01092273759534934</v>
       </c>
       <c r="M9" t="n">
-        <v>9.178802990061184</v>
+        <v>9.152911757684768</v>
       </c>
       <c r="N9" t="n">
-        <v>127.7686791290219</v>
+        <v>126.9610365992757</v>
       </c>
       <c r="O9" t="n">
-        <v>11.30348084127283</v>
+        <v>11.26769881560897</v>
       </c>
       <c r="P9" t="n">
-        <v>145.3312712601297</v>
+        <v>145.3171812226628</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22488,28 +22561,28 @@
         <v>0.0822</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3945223492267224</v>
+        <v>-0.3912582396552202</v>
       </c>
       <c r="J10" t="n">
+        <v>291</v>
+      </c>
+      <c r="K10" t="n">
         <v>290</v>
       </c>
-      <c r="K10" t="n">
-        <v>289</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.05127376016901419</v>
+        <v>0.05094331672557062</v>
       </c>
       <c r="M10" t="n">
-        <v>10.22718106049777</v>
+        <v>10.20820497658387</v>
       </c>
       <c r="N10" t="n">
-        <v>159.4978364339157</v>
+        <v>158.6396205241155</v>
       </c>
       <c r="O10" t="n">
-        <v>12.62924528362308</v>
+        <v>12.59522213079688</v>
       </c>
       <c r="P10" t="n">
-        <v>154.5060261098245</v>
+        <v>154.4716310299321</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22560,28 +22633,28 @@
         <v>0.081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3631701990445362</v>
+        <v>-0.3664196583702082</v>
       </c>
       <c r="J11" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K11" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04875413325811195</v>
+        <v>0.05025898236579096</v>
       </c>
       <c r="M11" t="n">
-        <v>9.513593317195292</v>
+        <v>9.46452349730604</v>
       </c>
       <c r="N11" t="n">
-        <v>141.426736755804</v>
+        <v>140.0546208972551</v>
       </c>
       <c r="O11" t="n">
-        <v>11.89229737081124</v>
+        <v>11.83446749529759</v>
       </c>
       <c r="P11" t="n">
-        <v>159.6654039369547</v>
+        <v>159.699349986776</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22632,28 +22705,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4733129450890591</v>
+        <v>-0.476088921965908</v>
       </c>
       <c r="J12" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K12" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06896541667405154</v>
+        <v>0.07052879563748382</v>
       </c>
       <c r="M12" t="n">
-        <v>10.60882711112677</v>
+        <v>10.55863945599156</v>
       </c>
       <c r="N12" t="n">
-        <v>166.2114674165556</v>
+        <v>164.8898911402704</v>
       </c>
       <c r="O12" t="n">
-        <v>12.89230264214099</v>
+        <v>12.84094588183715</v>
       </c>
       <c r="P12" t="n">
-        <v>167.6700993717562</v>
+        <v>167.6990726671349</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22704,28 +22777,28 @@
         <v>0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4281046262525983</v>
+        <v>-0.4308427323556759</v>
       </c>
       <c r="J13" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K13" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0647278864050691</v>
+        <v>0.06633685835052094</v>
       </c>
       <c r="M13" t="n">
-        <v>9.995275594320864</v>
+        <v>9.947496985066568</v>
       </c>
       <c r="N13" t="n">
-        <v>147.7954979183663</v>
+        <v>146.4524798369161</v>
       </c>
       <c r="O13" t="n">
-        <v>12.15711717136782</v>
+        <v>12.10175523785356</v>
       </c>
       <c r="P13" t="n">
-        <v>172.132900989001</v>
+        <v>172.1611247451314</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22776,28 +22849,28 @@
         <v>0.1459</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4997498701273109</v>
+        <v>-0.5001051564364621</v>
       </c>
       <c r="J14" t="n">
+        <v>291</v>
+      </c>
+      <c r="K14" t="n">
         <v>290</v>
       </c>
-      <c r="K14" t="n">
-        <v>289</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.09508327684150508</v>
+        <v>0.09588438649307462</v>
       </c>
       <c r="M14" t="n">
-        <v>9.284390682365807</v>
+        <v>9.253938915997709</v>
       </c>
       <c r="N14" t="n">
-        <v>131.6363052820896</v>
+        <v>131.1832766844562</v>
       </c>
       <c r="O14" t="n">
-        <v>11.47328659461139</v>
+        <v>11.45352682296838</v>
       </c>
       <c r="P14" t="n">
-        <v>174.4970209920316</v>
+        <v>174.5007437306038</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22848,28 +22921,28 @@
         <v>0.1054</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5437871886869526</v>
+        <v>-0.5518158311145627</v>
       </c>
       <c r="J15" t="n">
+        <v>291</v>
+      </c>
+      <c r="K15" t="n">
         <v>290</v>
       </c>
-      <c r="K15" t="n">
-        <v>289</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1120992384615244</v>
+        <v>0.116416068505715</v>
       </c>
       <c r="M15" t="n">
-        <v>9.394524680963935</v>
+        <v>9.342742485429955</v>
       </c>
       <c r="N15" t="n">
-        <v>129.7136081581437</v>
+        <v>128.5591305231942</v>
       </c>
       <c r="O15" t="n">
-        <v>11.38918821330755</v>
+        <v>11.33839188435442</v>
       </c>
       <c r="P15" t="n">
-        <v>172.9177244993399</v>
+        <v>173.0015165969882</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22920,28 +22993,28 @@
         <v>0.1497</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4355869320802928</v>
+        <v>-0.4393791703485389</v>
       </c>
       <c r="J16" t="n">
+        <v>291</v>
+      </c>
+      <c r="K16" t="n">
         <v>290</v>
       </c>
-      <c r="K16" t="n">
-        <v>289</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.09239319883947394</v>
+        <v>0.09489024277431957</v>
       </c>
       <c r="M16" t="n">
-        <v>8.11871451600603</v>
+        <v>8.069750841499953</v>
       </c>
       <c r="N16" t="n">
-        <v>103.2222336977032</v>
+        <v>102.4326366924217</v>
       </c>
       <c r="O16" t="n">
-        <v>10.15983433416624</v>
+        <v>10.12090098224569</v>
       </c>
       <c r="P16" t="n">
-        <v>173.0997159337404</v>
+        <v>173.1392186971755</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -22992,28 +23065,28 @@
         <v>0.1574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4514019903170784</v>
+        <v>-0.4497248652586947</v>
       </c>
       <c r="J17" t="n">
+        <v>291</v>
+      </c>
+      <c r="K17" t="n">
         <v>290</v>
       </c>
-      <c r="K17" t="n">
-        <v>289</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1551483130228856</v>
+        <v>0.1551604906746559</v>
       </c>
       <c r="M17" t="n">
-        <v>6.439424294423826</v>
+        <v>6.42648773217558</v>
       </c>
       <c r="N17" t="n">
-        <v>61.45060848256191</v>
+        <v>61.25853495172962</v>
       </c>
       <c r="O17" t="n">
-        <v>7.839043850021628</v>
+        <v>7.826783180319334</v>
       </c>
       <c r="P17" t="n">
-        <v>179.661072062866</v>
+        <v>179.643498916971</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23064,28 +23137,28 @@
         <v>0.1052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3584722375527554</v>
+        <v>-0.3593957703746117</v>
       </c>
       <c r="J18" t="n">
+        <v>291</v>
+      </c>
+      <c r="K18" t="n">
         <v>290</v>
       </c>
-      <c r="K18" t="n">
-        <v>289</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1166861890386839</v>
+        <v>0.1180218847968473</v>
       </c>
       <c r="M18" t="n">
-        <v>5.776529071721948</v>
+        <v>5.761031822811564</v>
       </c>
       <c r="N18" t="n">
-        <v>53.87315978335264</v>
+        <v>53.69340185997736</v>
       </c>
       <c r="O18" t="n">
-        <v>7.339833770825647</v>
+        <v>7.327578171536443</v>
       </c>
       <c r="P18" t="n">
-        <v>188.1598563006206</v>
+        <v>188.1695332039238</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23123,7 +23196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S291"/>
+  <dimension ref="A1:S292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51180,12 +51253,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>-46.28992265685902,167.7313435195776</t>
+          <t>-46.28992534245136,167.73138388712405</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>-46.28921398234368,167.73154240396926</t>
+          <t>-46.28921702080897,167.7315881886978</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -51195,17 +51268,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>-46.28779198154938,167.7318671323482</t>
+          <t>-46.287795078700206,167.7319136886917</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>-46.28707531803697,167.73194619537108</t>
+          <t>-46.28707813374876,167.7319886252371</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>-46.28634976187545,167.7320643040569</t>
+          <t>-46.286351042947935,167.7320922266338</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -51215,27 +51288,27 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>-46.28491415474108,167.73216475202474</t>
+          <t>-46.28491757668048,167.7322393395708</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>-46.284193071621644,167.73214348860301</t>
+          <t>-46.284195906434064,167.73220527781694</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>-46.28344794659858,167.73205860116127</t>
+          <t>-46.283446282571376,167.73215689809814</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>-46.28273034851212,167.7319905319634</t>
+          <t>-46.28272878314935,167.7320829998017</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>-46.28198928126559,167.7318271361438</t>
+          <t>-46.2819767958153,167.73191944468138</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -51245,12 +51318,12 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>-46.28056104427198,167.73146078469514</t>
+          <t>-46.28054210099303,167.73156410401273</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>-46.279865609678815,167.73120045481738</t>
+          <t>-46.27985239883556,167.7312725952787</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
@@ -51264,6 +51337,103 @@
         </is>
       </c>
       <c r="S291" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-46.28992608034327,167.7313949785275</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-46.289216473030656,167.73157993454905</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>-46.288494067861606,167.73157025382707</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-46.28780224239804,167.7320213744434</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-46.28707839905819,167.73199262318832</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-46.28634804190631,167.732026815415</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>-46.28562387466719,167.73193833480232</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>-46.28491975910524,167.73228691014455</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-46.28419995695558,167.73229356660528</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-46.28344393875765,167.73229534266648</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-46.28272677481456,167.73220162801067</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-46.28195848024336,167.73205485590097</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-46.28124762304619,167.73189793951738</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-46.28051367441224,167.731719145487</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>-46.27983446320549,167.73137053592473</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>-46.279158827727976,167.73100172610702</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>-46.27848095979171,167.73065143522965</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0597/nzd0597.xlsx
+++ b/data/nzd0597/nzd0597.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S292"/>
+  <dimension ref="A1:S293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18706,13 +18706,13 @@
         <v>163.46</v>
       </c>
       <c r="D291" t="n">
-        <v>163.26</v>
+        <v>159.11</v>
       </c>
       <c r="E291" t="n">
-        <v>153.56</v>
+        <v>157.17</v>
       </c>
       <c r="F291" t="n">
-        <v>155.42</v>
+        <v>158.71</v>
       </c>
       <c r="G291" t="n">
         <v>153.1</v>
@@ -18769,19 +18769,19 @@
         <v>164.1</v>
       </c>
       <c r="D292" t="n">
-        <v>172.52</v>
+        <v>161.14</v>
       </c>
       <c r="E292" t="n">
-        <v>145.21</v>
+        <v>171.88</v>
       </c>
       <c r="F292" t="n">
-        <v>155.11</v>
+        <v>178.49</v>
       </c>
       <c r="G292" t="n">
         <v>158.16</v>
       </c>
       <c r="H292" t="n">
-        <v>170.3</v>
+        <v>146.74</v>
       </c>
       <c r="I292" t="n">
         <v>148.63</v>
@@ -18814,6 +18814,69 @@
         <v>177.28</v>
       </c>
       <c r="S292" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>171.69</v>
+      </c>
+      <c r="C293" t="n">
+        <v>164.47</v>
+      </c>
+      <c r="D293" t="n">
+        <v>164.01</v>
+      </c>
+      <c r="E293" t="n">
+        <v>167.46</v>
+      </c>
+      <c r="F293" t="n">
+        <v>174.45</v>
+      </c>
+      <c r="G293" t="n">
+        <v>157.54</v>
+      </c>
+      <c r="H293" t="n">
+        <v>144.78</v>
+      </c>
+      <c r="I293" t="n">
+        <v>148.34</v>
+      </c>
+      <c r="J293" t="n">
+        <v>153.58</v>
+      </c>
+      <c r="K293" t="n">
+        <v>153.23</v>
+      </c>
+      <c r="L293" t="n">
+        <v>157.73</v>
+      </c>
+      <c r="M293" t="n">
+        <v>163.26</v>
+      </c>
+      <c r="N293" t="n">
+        <v>161.73</v>
+      </c>
+      <c r="O293" t="n">
+        <v>156.45</v>
+      </c>
+      <c r="P293" t="n">
+        <v>163.16</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>171.22</v>
+      </c>
+      <c r="R293" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="S293" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18830,7 +18893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21823,6 +21886,16 @@
       </c>
       <c r="B299" t="n">
         <v>0.18</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>
@@ -21985,28 +22058,28 @@
         <v>0.0317</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7228505955924062</v>
+        <v>-0.7081214151620102</v>
       </c>
       <c r="J2" t="n">
+        <v>292</v>
+      </c>
+      <c r="K2" t="n">
         <v>291</v>
       </c>
-      <c r="K2" t="n">
-        <v>290</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1099198458024514</v>
+        <v>0.1060832572943193</v>
       </c>
       <c r="M2" t="n">
-        <v>12.64060558360327</v>
+        <v>12.66651302450197</v>
       </c>
       <c r="N2" t="n">
-        <v>235.358467640048</v>
+        <v>236.0843521096723</v>
       </c>
       <c r="O2" t="n">
-        <v>15.34139718669874</v>
+        <v>15.3650366777848</v>
       </c>
       <c r="P2" t="n">
-        <v>169.7728918569418</v>
+        <v>169.6179916642195</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22057,28 +22130,28 @@
         <v>0.0347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8033083837040668</v>
+        <v>-0.789778981032611</v>
       </c>
       <c r="J3" t="n">
+        <v>292</v>
+      </c>
+      <c r="K3" t="n">
         <v>291</v>
       </c>
-      <c r="K3" t="n">
-        <v>290</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1706228564936815</v>
+        <v>0.1659312931600224</v>
       </c>
       <c r="M3" t="n">
-        <v>11.00071491381133</v>
+        <v>11.02429514365386</v>
       </c>
       <c r="N3" t="n">
-        <v>174.4854377021252</v>
+        <v>175.1806737841652</v>
       </c>
       <c r="O3" t="n">
-        <v>13.20929361101967</v>
+        <v>13.23558362083687</v>
       </c>
       <c r="P3" t="n">
-        <v>166.4317440492501</v>
+        <v>166.2894613817841</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22129,28 +22202,28 @@
         <v>0.0341</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4813031668952675</v>
+        <v>-0.4771382511381435</v>
       </c>
       <c r="J4" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0477460308251243</v>
+        <v>0.04746795887944832</v>
       </c>
       <c r="M4" t="n">
-        <v>12.09657272850583</v>
+        <v>12.07194942303385</v>
       </c>
       <c r="N4" t="n">
-        <v>255.0359266731301</v>
+        <v>253.3042838721445</v>
       </c>
       <c r="O4" t="n">
-        <v>15.96984429082294</v>
+        <v>15.91553592789588</v>
       </c>
       <c r="P4" t="n">
-        <v>155.5462938478941</v>
+        <v>155.5016420235313</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22201,28 +22274,28 @@
         <v>0.0318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3446391600299468</v>
+        <v>-0.3076287532449577</v>
       </c>
       <c r="J5" t="n">
+        <v>292</v>
+      </c>
+      <c r="K5" t="n">
         <v>291</v>
       </c>
-      <c r="K5" t="n">
-        <v>290</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.03719973633624707</v>
+        <v>0.02930937933111244</v>
       </c>
       <c r="M5" t="n">
-        <v>10.484721860077</v>
+        <v>10.624328172165</v>
       </c>
       <c r="N5" t="n">
-        <v>171.0036259219246</v>
+        <v>175.1175136702985</v>
       </c>
       <c r="O5" t="n">
-        <v>13.07683547047697</v>
+        <v>13.23319740917887</v>
       </c>
       <c r="P5" t="n">
-        <v>153.2663475603853</v>
+        <v>152.8780791683629</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22273,28 +22346,28 @@
         <v>0.0353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2403750165554847</v>
+        <v>-0.2024362256453393</v>
       </c>
       <c r="J6" t="n">
+        <v>292</v>
+      </c>
+      <c r="K6" t="n">
         <v>291</v>
       </c>
-      <c r="K6" t="n">
-        <v>290</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02289495576684197</v>
+        <v>0.01577002455625076</v>
       </c>
       <c r="M6" t="n">
-        <v>9.573129864444192</v>
+        <v>9.750647246997319</v>
       </c>
       <c r="N6" t="n">
-        <v>137.1702199063151</v>
+        <v>142.903281320429</v>
       </c>
       <c r="O6" t="n">
-        <v>11.71196908748973</v>
+        <v>11.95421604792338</v>
       </c>
       <c r="P6" t="n">
-        <v>152.5549165995405</v>
+        <v>152.1567754417276</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22345,28 +22418,28 @@
         <v>0.0428</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1795352456612233</v>
+        <v>-0.1690425642082225</v>
       </c>
       <c r="J7" t="n">
+        <v>292</v>
+      </c>
+      <c r="K7" t="n">
         <v>291</v>
       </c>
-      <c r="K7" t="n">
-        <v>290</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01376739567208574</v>
+        <v>0.01224605644325438</v>
       </c>
       <c r="M7" t="n">
-        <v>9.231439119151347</v>
+        <v>9.248235728544415</v>
       </c>
       <c r="N7" t="n">
-        <v>128.441904487815</v>
+        <v>128.7793353866138</v>
       </c>
       <c r="O7" t="n">
-        <v>11.33322127586923</v>
+        <v>11.34809831586834</v>
       </c>
       <c r="P7" t="n">
-        <v>147.1996198314412</v>
+        <v>147.0892730007452</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22417,28 +22490,28 @@
         <v>0.0674</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03791272887471819</v>
+        <v>-0.04794022169235806</v>
       </c>
       <c r="J8" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K8" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000474262030037198</v>
+        <v>0.0007801205223683105</v>
       </c>
       <c r="M8" t="n">
-        <v>10.45915878048231</v>
+        <v>10.38014266702853</v>
       </c>
       <c r="N8" t="n">
-        <v>167.2222734145605</v>
+        <v>163.2204116698694</v>
       </c>
       <c r="O8" t="n">
-        <v>12.93144514022159</v>
+        <v>12.7757744058773</v>
       </c>
       <c r="P8" t="n">
-        <v>136.7829834673171</v>
+        <v>136.8884428141151</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22489,28 +22562,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1593718695555785</v>
+        <v>-0.1542861308759014</v>
       </c>
       <c r="J9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01092273759534934</v>
+        <v>0.0103094842705308</v>
       </c>
       <c r="M9" t="n">
-        <v>9.152911757684768</v>
+        <v>9.145254577640314</v>
       </c>
       <c r="N9" t="n">
-        <v>126.9610365992757</v>
+        <v>126.7042767663436</v>
       </c>
       <c r="O9" t="n">
-        <v>11.26769881560897</v>
+        <v>11.25629942593673</v>
       </c>
       <c r="P9" t="n">
-        <v>145.3171812226628</v>
+        <v>145.2633726615938</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22561,28 +22634,28 @@
         <v>0.0822</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3912582396552202</v>
+        <v>-0.3846257603140113</v>
       </c>
       <c r="J10" t="n">
+        <v>292</v>
+      </c>
+      <c r="K10" t="n">
         <v>291</v>
       </c>
-      <c r="K10" t="n">
-        <v>290</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.05094331672557062</v>
+        <v>0.04959265722204631</v>
       </c>
       <c r="M10" t="n">
-        <v>10.20820497658387</v>
+        <v>10.20626175511022</v>
       </c>
       <c r="N10" t="n">
-        <v>158.6396205241155</v>
+        <v>158.4056470463935</v>
       </c>
       <c r="O10" t="n">
-        <v>12.59522213079688</v>
+        <v>12.58593051968719</v>
       </c>
       <c r="P10" t="n">
-        <v>154.4716310299321</v>
+        <v>154.4018802156872</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22633,28 +22706,28 @@
         <v>0.081</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3664196583702082</v>
+        <v>-0.3640970159883285</v>
       </c>
       <c r="J11" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K11" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05025898236579096</v>
+        <v>0.05001620128267836</v>
       </c>
       <c r="M11" t="n">
-        <v>9.46452349730604</v>
+        <v>9.44303852159303</v>
       </c>
       <c r="N11" t="n">
-        <v>140.0546208972551</v>
+        <v>139.6094331980933</v>
       </c>
       <c r="O11" t="n">
-        <v>11.83446749529759</v>
+        <v>11.81564357951328</v>
       </c>
       <c r="P11" t="n">
-        <v>159.699349986776</v>
+        <v>159.6747757700656</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22705,28 +22778,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.476088921965908</v>
+        <v>-0.4741618640947513</v>
       </c>
       <c r="J12" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K12" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07052879563748382</v>
+        <v>0.07050392052891774</v>
       </c>
       <c r="M12" t="n">
-        <v>10.55863945599156</v>
+        <v>10.53123830854986</v>
       </c>
       <c r="N12" t="n">
-        <v>164.8898911402704</v>
+        <v>164.347297829804</v>
       </c>
       <c r="O12" t="n">
-        <v>12.84094588183715</v>
+        <v>12.81980100585824</v>
       </c>
       <c r="P12" t="n">
-        <v>167.6990726671349</v>
+        <v>167.6786838470097</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22777,28 +22850,28 @@
         <v>0.1169</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4308427323556759</v>
+        <v>-0.4290416703901981</v>
       </c>
       <c r="J13" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K13" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06633685835052094</v>
+        <v>0.06629396080442218</v>
       </c>
       <c r="M13" t="n">
-        <v>9.947496985066568</v>
+        <v>9.921930855217809</v>
       </c>
       <c r="N13" t="n">
-        <v>146.4524798369161</v>
+        <v>145.9741224687021</v>
       </c>
       <c r="O13" t="n">
-        <v>12.10175523785356</v>
+        <v>12.08197510627721</v>
       </c>
       <c r="P13" t="n">
-        <v>172.1611247451314</v>
+        <v>172.1422992298381</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22849,28 +22922,28 @@
         <v>0.1459</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5001051564364621</v>
+        <v>-0.4996895092670329</v>
       </c>
       <c r="J14" t="n">
+        <v>292</v>
+      </c>
+      <c r="K14" t="n">
         <v>291</v>
       </c>
-      <c r="K14" t="n">
-        <v>290</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.09588438649307462</v>
+        <v>0.0964227930846141</v>
       </c>
       <c r="M14" t="n">
-        <v>9.253938915997709</v>
+        <v>9.22440343677053</v>
       </c>
       <c r="N14" t="n">
-        <v>131.1832766844562</v>
+        <v>130.7336971536145</v>
       </c>
       <c r="O14" t="n">
-        <v>11.45352682296838</v>
+        <v>11.43388373010739</v>
       </c>
       <c r="P14" t="n">
-        <v>174.5007437306038</v>
+        <v>174.49637255551</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22921,28 +22994,28 @@
         <v>0.1054</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5518158311145627</v>
+        <v>-0.5530575264892085</v>
       </c>
       <c r="J15" t="n">
+        <v>292</v>
+      </c>
+      <c r="K15" t="n">
         <v>291</v>
       </c>
-      <c r="K15" t="n">
-        <v>290</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.116416068505715</v>
+        <v>0.1176849473346359</v>
       </c>
       <c r="M15" t="n">
-        <v>9.342742485429955</v>
+        <v>9.316377939688762</v>
       </c>
       <c r="N15" t="n">
-        <v>128.5591305231942</v>
+        <v>128.1282531797196</v>
       </c>
       <c r="O15" t="n">
-        <v>11.33839188435442</v>
+        <v>11.31937512320003</v>
       </c>
       <c r="P15" t="n">
-        <v>173.0015165969882</v>
+        <v>173.014574951032</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -22993,28 +23066,28 @@
         <v>0.1497</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4393791703485389</v>
+        <v>-0.4381533346786458</v>
       </c>
       <c r="J16" t="n">
+        <v>292</v>
+      </c>
+      <c r="K16" t="n">
         <v>291</v>
       </c>
-      <c r="K16" t="n">
-        <v>290</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.09489024277431957</v>
+        <v>0.09507726498435531</v>
       </c>
       <c r="M16" t="n">
-        <v>8.069750841499953</v>
+        <v>8.048626358459897</v>
       </c>
       <c r="N16" t="n">
-        <v>102.4326366924217</v>
+        <v>102.0912642819882</v>
       </c>
       <c r="O16" t="n">
-        <v>10.12090098224569</v>
+        <v>10.10402218336778</v>
       </c>
       <c r="P16" t="n">
-        <v>173.1392186971755</v>
+        <v>173.1263271325423</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -23065,28 +23138,28 @@
         <v>0.1574</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4497248652586947</v>
+        <v>-0.4472290766837117</v>
       </c>
       <c r="J17" t="n">
+        <v>292</v>
+      </c>
+      <c r="K17" t="n">
         <v>291</v>
       </c>
-      <c r="K17" t="n">
-        <v>290</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.1551604906746559</v>
+        <v>0.154638937590997</v>
       </c>
       <c r="M17" t="n">
-        <v>6.42648773217558</v>
+        <v>6.418037378562015</v>
       </c>
       <c r="N17" t="n">
-        <v>61.25853495172962</v>
+        <v>61.09208764285143</v>
       </c>
       <c r="O17" t="n">
-        <v>7.826783180319334</v>
+        <v>7.81614275988172</v>
       </c>
       <c r="P17" t="n">
-        <v>179.643498916971</v>
+        <v>179.6172518265041</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -23137,28 +23210,28 @@
         <v>0.1052</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3593957703746117</v>
+        <v>-0.3588486690283394</v>
       </c>
       <c r="J18" t="n">
+        <v>292</v>
+      </c>
+      <c r="K18" t="n">
         <v>291</v>
       </c>
-      <c r="K18" t="n">
-        <v>290</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.1180218847968473</v>
+        <v>0.1185204584219279</v>
       </c>
       <c r="M18" t="n">
-        <v>5.761031822811564</v>
+        <v>5.744005906005762</v>
       </c>
       <c r="N18" t="n">
-        <v>53.69340185997736</v>
+        <v>53.51100581409894</v>
       </c>
       <c r="O18" t="n">
-        <v>7.327578171536443</v>
+        <v>7.315121722439001</v>
       </c>
       <c r="P18" t="n">
-        <v>188.1695332039238</v>
+        <v>188.1637795841364</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -23196,7 +23269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S292"/>
+  <dimension ref="A1:S293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51263,17 +51336,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>-46.28850201268929,167.73168967682852</t>
+          <t>-46.28850557323605,167.73174319795086</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>-46.287795078700206,167.7319136886917</t>
+          <t>-46.28779198154938,167.7318671323482</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>-46.28707813374876,167.7319886252371</t>
+          <t>-46.28707531803697,167.73194619537108</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -51360,17 +51433,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>-46.288494067861606,167.73157025382707</t>
+          <t>-46.28850383157411,167.73171701773805</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>-46.28780224239804,167.7320213744434</t>
+          <t>-46.28777936110871,167.7316774249925</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>-46.28707839905819,167.73199262318832</t>
+          <t>-46.28705838920324,167.7316911004311</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -51380,7 +51453,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>-46.28562387466719,167.73193833480232</t>
+          <t>-46.285637847646754,167.73224289374244</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -51434,6 +51507,103 @@
         </is>
       </c>
       <c r="S292" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:26:38+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-46.2899252909705,167.7313831133052</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>-46.28921615634604,167.7315751626194</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>-46.28850136921434,167.7316800043375</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-46.2877831532794,167.73173442746256</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-46.287061846907804,167.7317432027175</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-46.28634840962488,167.7320348302278</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-46.285639010048385,167.73226823057448</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>-46.28491993108897,167.73229065891283</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-46.284199856138166,167.73229136908031</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-46.28344401988405,167.73229055085258</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-46.28272668272637,167.73220706729543</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-46.28195732799061,167.73206337472632</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-46.28124946319828,167.7318843350007</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-46.28051693498427,167.73170136206187</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-46.27983774300112,167.73135262606664</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>-46.2791615340922,167.73098694751442</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>-46.27848560936215,167.73062547346933</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
